--- a/reportes/conciliacion_20260601.xlsx
+++ b/reportes/conciliacion_20260601.xlsx
@@ -278,16 +278,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -303,7 +295,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -311,30 +303,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -634,43 +608,43 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="2">
-        <v>45839</v>
+      <c r="A2" s="1">
+        <v>46144</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -695,8 +669,8 @@
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="2">
-        <v>45839</v>
+      <c r="A3" s="1">
+        <v>46144</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -721,8 +695,8 @@
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="2">
-        <v>45840</v>
+      <c r="A4" s="1">
+        <v>46145</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -747,8 +721,8 @@
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="2">
-        <v>45841</v>
+      <c r="A5" s="1">
+        <v>46146</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -782,8 +756,8 @@
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="2">
-        <v>45842</v>
+      <c r="A6" s="1">
+        <v>46147</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
@@ -808,8 +782,8 @@
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="2">
-        <v>45843</v>
+      <c r="A7" s="1">
+        <v>46148</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
@@ -834,8 +808,8 @@
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="2">
-        <v>45843</v>
+      <c r="A8" s="1">
+        <v>46148</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -860,8 +834,8 @@
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="2">
-        <v>45844</v>
+      <c r="A9" s="1">
+        <v>46149</v>
       </c>
       <c r="B9" t="s">
         <v>18</v>
@@ -886,8 +860,8 @@
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="2">
-        <v>45845</v>
+      <c r="A10" s="1">
+        <v>46150</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
@@ -921,8 +895,8 @@
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="2">
-        <v>45846</v>
+      <c r="A11" s="1">
+        <v>46151</v>
       </c>
       <c r="B11" t="s">
         <v>20</v>
@@ -956,8 +930,8 @@
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="2">
-        <v>45847</v>
+      <c r="A12" s="1">
+        <v>46152</v>
       </c>
       <c r="B12" t="s">
         <v>21</v>
@@ -982,8 +956,8 @@
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="2">
-        <v>45848</v>
+      <c r="A13" s="1">
+        <v>46153</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
@@ -1008,8 +982,8 @@
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="2">
-        <v>45849</v>
+      <c r="A14" s="1">
+        <v>46154</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
@@ -1034,8 +1008,8 @@
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="2">
-        <v>45850</v>
+      <c r="A15" s="1">
+        <v>46155</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
@@ -1060,8 +1034,8 @@
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="2">
-        <v>45851</v>
+      <c r="A16" s="1">
+        <v>46156</v>
       </c>
       <c r="B16" t="s">
         <v>25</v>
@@ -1086,8 +1060,8 @@
       </c>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="2">
-        <v>45852</v>
+      <c r="A17" s="1">
+        <v>46157</v>
       </c>
       <c r="B17" t="s">
         <v>26</v>
@@ -1112,8 +1086,8 @@
       </c>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="2">
-        <v>45853</v>
+      <c r="A18" s="1">
+        <v>46158</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -1138,8 +1112,8 @@
       </c>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="2">
-        <v>45853</v>
+      <c r="A19" s="1">
+        <v>46158</v>
       </c>
       <c r="B19" t="s">
         <v>28</v>
@@ -1164,8 +1138,8 @@
       </c>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="2">
-        <v>45854</v>
+      <c r="A20" s="1">
+        <v>46159</v>
       </c>
       <c r="B20" t="s">
         <v>29</v>
@@ -1190,8 +1164,8 @@
       </c>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="2">
-        <v>45855</v>
+      <c r="A21" s="1">
+        <v>46160</v>
       </c>
       <c r="B21" t="s">
         <v>30</v>
@@ -1225,8 +1199,8 @@
       </c>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="2">
-        <v>45856</v>
+      <c r="A22" s="1">
+        <v>46161</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
@@ -1251,8 +1225,8 @@
       </c>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="2">
-        <v>45858</v>
+      <c r="A23" s="1">
+        <v>46163</v>
       </c>
       <c r="B23" t="s">
         <v>32</v>
@@ -1277,8 +1251,8 @@
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="2">
-        <v>45858</v>
+      <c r="A24" s="1">
+        <v>46163</v>
       </c>
       <c r="B24" t="s">
         <v>33</v>
@@ -1303,8 +1277,8 @@
       </c>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="2">
-        <v>45858</v>
+      <c r="A25" s="1">
+        <v>46163</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
@@ -1329,8 +1303,8 @@
       </c>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="2">
-        <v>45860</v>
+      <c r="A26" s="1">
+        <v>46165</v>
       </c>
       <c r="B26" t="s">
         <v>35</v>
@@ -1355,8 +1329,8 @@
       </c>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="2">
-        <v>45863</v>
+      <c r="A27" s="1">
+        <v>46168</v>
       </c>
       <c r="B27" t="s">
         <v>36</v>
@@ -1381,8 +1355,8 @@
       </c>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="2">
-        <v>45865</v>
+      <c r="A28" s="1">
+        <v>46170</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
@@ -1407,8 +1381,8 @@
       </c>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="2">
-        <v>45866</v>
+      <c r="A29" s="1">
+        <v>46171</v>
       </c>
       <c r="B29" t="s">
         <v>38</v>
@@ -1433,8 +1407,8 @@
       </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="2">
-        <v>45866</v>
+      <c r="A30" s="1">
+        <v>46171</v>
       </c>
       <c r="B30" t="s">
         <v>39</v>
@@ -1459,8 +1433,8 @@
       </c>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="2">
-        <v>45869</v>
+      <c r="A31" s="1">
+        <v>46174</v>
       </c>
       <c r="B31" t="s">
         <v>40</v>
